--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2023_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2023_metropolitana.xlsx
@@ -108,12 +108,12 @@
     <t xml:space="preserve">Lo Espejo</t>
   </si>
   <si>
+    <t xml:space="preserve">El Bosque</t>
+  </si>
+  <si>
     <t xml:space="preserve">San Joaquín</t>
   </si>
   <si>
-    <t xml:space="preserve">El Bosque</t>
-  </si>
-  <si>
     <t xml:space="preserve">Buin</t>
   </si>
   <si>
@@ -156,12 +156,12 @@
     <t xml:space="preserve">Macul</t>
   </si>
   <si>
+    <t xml:space="preserve">Maipú</t>
+  </si>
+  <si>
     <t xml:space="preserve">Lampa</t>
   </si>
   <si>
-    <t xml:space="preserve">Maipú</t>
-  </si>
-  <si>
     <t xml:space="preserve">Quilicura</t>
   </si>
   <si>
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 20:35</t>
+    <t xml:space="preserve">2026-09-09 23:34</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -1039,7 +1039,7 @@
         <v>30</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>13129</v>
+        <v>13105</v>
       </c>
       <c r="D26" s="2" t="n">
         <v>2023</v>
@@ -1056,7 +1056,7 @@
         <v>31</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>13105</v>
+        <v>13129</v>
       </c>
       <c r="D27" s="2" t="n">
         <v>2023</v>
@@ -1311,7 +1311,7 @@
         <v>46</v>
       </c>
       <c r="C42" s="2" t="n">
-        <v>13302</v>
+        <v>13119</v>
       </c>
       <c r="D42" s="2" t="n">
         <v>2023</v>
@@ -1328,7 +1328,7 @@
         <v>47</v>
       </c>
       <c r="C43" s="2" t="n">
-        <v>13119</v>
+        <v>13302</v>
       </c>
       <c r="D43" s="2" t="n">
         <v>2023</v>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2023_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2023_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 23:34</t>
+    <t xml:space="preserve">2026-09-17 14:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2023_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2023_metropolitana.xlsx
@@ -87,12 +87,12 @@
     <t xml:space="preserve">Conchalí</t>
   </si>
   <si>
+    <t xml:space="preserve">La Granja</t>
+  </si>
+  <si>
     <t xml:space="preserve">Pirque</t>
   </si>
   <si>
-    <t xml:space="preserve">La Granja</t>
-  </si>
-  <si>
     <t xml:space="preserve">Pedro Aguirre Cerda</t>
   </si>
   <si>
@@ -171,12 +171,12 @@
     <t xml:space="preserve">Huechuraba</t>
   </si>
   <si>
+    <t xml:space="preserve">Lo Barnechea</t>
+  </si>
+  <si>
     <t xml:space="preserve">San Miguel</t>
   </si>
   <si>
-    <t xml:space="preserve">Lo Barnechea</t>
-  </si>
-  <si>
     <t xml:space="preserve">La Reina</t>
   </si>
   <si>
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-17 14:28</t>
+    <t xml:space="preserve">2026-09-23 12:55</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -920,7 +920,7 @@
         <v>23</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>13202</v>
+        <v>13111</v>
       </c>
       <c r="D19" s="2" t="n">
         <v>2023</v>
@@ -937,7 +937,7 @@
         <v>24</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>13111</v>
+        <v>13202</v>
       </c>
       <c r="D20" s="2" t="n">
         <v>2023</v>
@@ -1396,7 +1396,7 @@
         <v>51</v>
       </c>
       <c r="C47" s="2" t="n">
-        <v>13130</v>
+        <v>13115</v>
       </c>
       <c r="D47" s="2" t="n">
         <v>2023</v>
@@ -1413,7 +1413,7 @@
         <v>52</v>
       </c>
       <c r="C48" s="2" t="n">
-        <v>13115</v>
+        <v>13130</v>
       </c>
       <c r="D48" s="2" t="n">
         <v>2023</v>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2023_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2023_metropolitana.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="72">
   <si>
     <t xml:space="preserve">Región</t>
   </si>
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-23 12:55</t>
+    <t xml:space="preserve">2026-10-01 23:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -219,7 +219,7 @@
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
-    <t xml:space="preserve">Ingreso sobre salario mínimo (%)</t>
+    <t xml:space="preserve">% con ingreso igual al mínimo</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>
@@ -232,9 +232,6 @@
   </si>
   <si>
     <t xml:space="preserve">Unidad de medida</t>
-  </si>
-  <si>
-    <t xml:space="preserve">% sobre salario mínimo</t>
   </si>
 </sst>
 </file>
@@ -1584,7 +1581,7 @@
         <v>71</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2023_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2023_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 23:23</t>
+    <t xml:space="preserve">2026-10-02 11:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2023_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2023_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 11:28</t>
+    <t xml:space="preserve">2026-10-02 15:22</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_i_peringrmin_a_2023_metropolitana.xlsx
+++ b/output/graficos_dimensiones/comunal_i_peringrmin_a_2023_metropolitana.xlsx
@@ -201,7 +201,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 15:22</t>
+    <t xml:space="preserve">2026-10-05 12:55</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
